--- a/feature_list.xlsx
+++ b/feature_list.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:F122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,12 +407,15 @@
         <v>機能</v>
       </c>
       <c r="C1" t="str">
+        <v>本番実装済</v>
+      </c>
+      <c r="D1" t="str">
         <v>モック実装済</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>実装検討</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>備考</v>
       </c>
     </row>
@@ -420,18 +423,6 @@
       <c r="A2" t="str">
         <v>イベント（toC）</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -440,13 +431,10 @@
       <c r="B3" t="str">
         <v>大会検索（リスト表示）</v>
       </c>
-      <c r="C3" t="str">
-        <v>✓</v>
-      </c>
       <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F3" t="str">
         <v>検索バー＋詳細設定アコーディオン</v>
       </c>
     </row>
@@ -457,14 +445,8 @@
       <c r="B4" t="str">
         <v>検索フィルター（タイトル・レギュ・エリア）</v>
       </c>
-      <c r="C4" t="str">
-        <v>✓</v>
-      </c>
       <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="5">
@@ -474,14 +456,8 @@
       <c r="B5" t="str">
         <v>参加予定イベント一覧</v>
       </c>
-      <c r="C5" t="str">
-        <v>✓</v>
-      </c>
       <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="6">
@@ -491,13 +467,10 @@
       <c r="B6" t="str">
         <v>おすすめイベント表示</v>
       </c>
-      <c r="C6" t="str">
-        <v>✓</v>
-      </c>
       <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F6" t="str">
         <v>将来的に広告メニュー化</v>
       </c>
     </row>
@@ -508,13 +481,10 @@
       <c r="B7" t="str">
         <v>イベント詳細表示</v>
       </c>
-      <c r="C7" t="str">
-        <v>✓</v>
-      </c>
       <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F7" t="str">
         <v>大会情報・定員・参加費等</v>
       </c>
     </row>
@@ -525,14 +495,8 @@
       <c r="B8" t="str">
         <v>参加登録（ワンタップ）</v>
       </c>
-      <c r="C8" t="str">
-        <v>✓</v>
-      </c>
       <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +506,10 @@
       <c r="B9" t="str">
         <v>チェックイン</v>
       </c>
-      <c r="C9" t="str">
-        <v>✓</v>
-      </c>
       <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F9" t="str">
         <v>LINE IDベースで自動CRM蓄積</v>
       </c>
     </row>
@@ -559,13 +520,10 @@
       <c r="B10" t="str">
         <v>デッキ選択して参加登録</v>
       </c>
-      <c r="C10" t="str">
-        <v>✓</v>
-      </c>
       <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F10" t="str">
         <v>スナップショット保存</v>
       </c>
     </row>
@@ -576,13 +534,10 @@
       <c r="B11" t="str">
         <v>問い合わせ（ジャッジ/主催者/運営）</v>
       </c>
-      <c r="C11" t="str">
-        <v>✓</v>
-      </c>
       <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F11" t="str">
         <v>大会ページ内に配置</v>
       </c>
     </row>
@@ -593,13 +548,10 @@
       <c r="B12" t="str">
         <v>大会検索（地図ベース）</v>
       </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v>候補</v>
-      </c>
       <c r="E12" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F12" t="str">
         <v>近くの店舗の大会を地図で探す</v>
       </c>
     </row>
@@ -610,14 +562,11 @@
       <c r="B13" t="str">
         <v>大会リマインド通知</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>候補</v>
-      </c>
       <c r="E13" t="str">
-        <v>LINE push通知経由</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>LINE push通知経由。ドタキャン対策＋リテンション向上</v>
       </c>
     </row>
     <row r="14">
@@ -627,13 +576,10 @@
       <c r="B14" t="str">
         <v>デポジット支払い（予約）</v>
       </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>候補</v>
-      </c>
       <c r="E14" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F14" t="str">
         <v>ドタキャン対策。toB プロプラン連動</v>
       </c>
     </row>
@@ -644,13 +590,10 @@
       <c r="B15" t="str">
         <v>大会レビュー・評価</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>候補</v>
-      </c>
       <c r="E15" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F15" t="str">
         <v>店舗・大会の質の可視化</v>
       </c>
     </row>
@@ -658,18 +601,6 @@
       <c r="A16" t="str">
         <v>大会進行（LIVE）</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -678,13 +609,10 @@
       <c r="B17" t="str">
         <v>マッチング結果表示（リアルタイム）</v>
       </c>
-      <c r="C17" t="str">
-        <v>✓</v>
-      </c>
       <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F17" t="str">
         <v>対戦相手・テーブル番号</v>
       </c>
     </row>
@@ -695,13 +623,10 @@
       <c r="B18" t="str">
         <v>ラウンド進行バー</v>
       </c>
-      <c r="C18" t="str">
-        <v>✓</v>
-      </c>
       <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F18" t="str">
         <v>大会全体の進捗可視化</v>
       </c>
     </row>
@@ -712,14 +637,8 @@
       <c r="B19" t="str">
         <v>対戦開始ボタン</v>
       </c>
-      <c r="C19" t="str">
-        <v>✓</v>
-      </c>
       <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="20">
@@ -729,14 +648,8 @@
       <c r="B20" t="str">
         <v>対戦結果入力（勝敗＋先攻後攻）</v>
       </c>
-      <c r="C20" t="str">
-        <v>✓</v>
-      </c>
       <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="21">
@@ -746,13 +659,10 @@
       <c r="B21" t="str">
         <v>大会終了時の最終成績表示</v>
       </c>
-      <c r="C21" t="str">
-        <v>✓</v>
-      </c>
       <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F21" t="str">
         <v>全ラウンドの対戦履歴一覧</v>
       </c>
     </row>
@@ -763,13 +673,10 @@
       <c r="B22" t="str">
         <v>大会中の問い合わせ機能</v>
       </c>
-      <c r="C22" t="str">
-        <v>✓</v>
-      </c>
       <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
+        <v>✓</v>
+      </c>
+      <c r="F22" t="str">
         <v>ジャッジ・主催者への連絡</v>
       </c>
     </row>
@@ -780,13 +687,10 @@
       <c r="B23" t="str">
         <v>順位表・スタンディング表示</v>
       </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>候補</v>
-      </c>
       <c r="E23" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F23" t="str">
         <v>リアルタイム順位確認</v>
       </c>
     </row>
@@ -797,150 +701,105 @@
       <c r="B24" t="str">
         <v>対戦相手のプロフィール閲覧</v>
       </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v>候補</v>
-      </c>
       <c r="E24" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F24" t="str">
         <v>戦績・使用デッキ等</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>戦績（toC）</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
+        <v>GG・評価システム（チェックイン限定）</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B26" t="str">
-        <v>大会参加履歴一覧</v>
-      </c>
-      <c r="C26" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
+        <v>GGボタン（いい勝負だったね！）</v>
       </c>
       <c r="E26" t="str">
-        <v>大会名・日付・成績・順位・使用デッキ</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>コアループのRetention施策。大会チェックイン者のみ。相互に押すとGG成立</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B27" t="str">
-        <v>大会参加時のデッキスナップショット保存</v>
-      </c>
-      <c r="C27" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
+        <v>GG成立の遅延開示（3日後）</v>
       </c>
       <c r="E27" t="str">
-        <v>削除しても閲覧可</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>マッチング型。プレッシャー排除。遅延期間はABテスト検証候補</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B28" t="str">
-        <v>外部大会スクショアップロード（OCR）</v>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
+        <v>GGポイント累積</v>
+      </c>
+      <c r="E28" t="str">
         <v>Phase1</v>
       </c>
-      <c r="E28" t="str">
-        <v>メーカーID突合でLevel 2信頼性付与</v>
+      <c r="F28" t="str">
+        <v>勝敗に関係ない指標。成立相手は非公開。プロフィールに表示</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B29" t="str">
-        <v>手動入力フォーム（自己申告記録）</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
+        <v>グッドマナーボタン</v>
+      </c>
+      <c r="E29" t="str">
         <v>Phase1</v>
       </c>
-      <c r="E29" t="str">
-        <v>Level 3信頼性。招待制エビデンス不可</v>
+      <c r="F29" t="str">
+        <v>対戦相手の人間性への評価。コミュニティの自浄作用</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B30" t="str">
-        <v>累積スタッツ（通算勝率・大会数等）</v>
-      </c>
-      <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="D30" t="str">
-        <v>候補</v>
+        <v>グッドオーガナイザーボタン</v>
       </c>
       <c r="E30" t="str">
-        <v>サブスク機能候補</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>大会主催者への感謝。運営品質の可視化。toB協賛キャンペーン連動</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>戦績</v>
+        <v>GG・評価</v>
       </c>
       <c r="B31" t="str">
-        <v>勝率推移グラフ</v>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v>候補</v>
+        <v>GG・マナー・オーガナイザーのプロフィール表示</v>
       </c>
       <c r="E31" t="str">
-        <v>サブスク機能候補</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>勝率以外の多面的プレイヤー評価。ショーケースにも反映</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>戦績</v>
-      </c>
-      <c r="B32" t="str">
-        <v>先攻/後攻別勝率</v>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E32" t="str">
-        <v>サブスク機能候補</v>
+        <v>戦績（toC）</v>
       </c>
     </row>
     <row r="33">
@@ -948,16 +807,13 @@
         <v>戦績</v>
       </c>
       <c r="B33" t="str">
-        <v>対デッキタイプ別勝率</v>
-      </c>
-      <c r="C33" t="str">
-        <v/>
+        <v>大会参加履歴一覧</v>
       </c>
       <c r="D33" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E33" t="str">
-        <v>サブスク機能候補。デッキ登録機能後</v>
+        <v>✓</v>
+      </c>
+      <c r="F33" t="str">
+        <v>大会名・日付・成績・順位・使用デッキ</v>
       </c>
     </row>
     <row r="34">
@@ -965,16 +821,13 @@
         <v>戦績</v>
       </c>
       <c r="B34" t="str">
-        <v>月別・タイトル別スタッツ</v>
-      </c>
-      <c r="C34" t="str">
-        <v/>
+        <v>大会参加時のデッキスナップショット保存</v>
       </c>
       <c r="D34" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E34" t="str">
-        <v>サブスク機能候補</v>
+        <v>✓</v>
+      </c>
+      <c r="F34" t="str">
+        <v>削除しても閲覧可</v>
       </c>
     </row>
     <row r="35">
@@ -982,594 +835,441 @@
         <v>戦績</v>
       </c>
       <c r="B35" t="str">
-        <v>バッジ・実績（100大会参加等）</v>
-      </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
-      <c r="D35" t="str">
-        <v>候補</v>
+        <v>外部大会スクショアップロード（OCR）</v>
       </c>
       <c r="E35" t="str">
-        <v>エンゲージメント向上</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>メーカーID突合でLevel 2信頼性付与</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>アーキタイプ・メタゲーム分析</v>
+        <v>戦績</v>
       </c>
       <c r="B36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
-        <v/>
-      </c>
-      <c r="D36" t="str">
-        <v/>
+        <v>手動入力フォーム（自己申告記録）</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>Phase1</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Level 3信頼性。招待制エビデンス不可</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B37" t="str">
-        <v>自分の使用アーキタイプ登録（任意選択）</v>
-      </c>
-      <c r="C37" t="str">
-        <v/>
-      </c>
-      <c r="D37" t="str">
-        <v>候補</v>
+        <v>累積スタッツ（通算勝率・大会数等）</v>
       </c>
       <c r="E37" t="str">
-        <v>大会参加時にプルダウンで選択</v>
+        <v>候補</v>
+      </c>
+      <c r="F37" t="str">
+        <v>サブスク機能候補</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B38" t="str">
-        <v>対戦相手のアーキタイプ入力（任意）</v>
-      </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-      <c r="D38" t="str">
-        <v>候補</v>
+        <v>勝率推移グラフ</v>
       </c>
       <c r="E38" t="str">
-        <v>対戦結果入力時に追加フィールド</v>
+        <v>候補</v>
+      </c>
+      <c r="F38" t="str">
+        <v>サブスク機能候補</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B39" t="str">
-        <v>対アーキタイプ別勝率</v>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39" t="str">
-        <v>候補</v>
+        <v>先攻/後攻別勝率</v>
       </c>
       <c r="E39" t="str">
-        <v>サブスク機能。個人レベルの対面別分析</v>
+        <v>候補</v>
+      </c>
+      <c r="F39" t="str">
+        <v>サブスク機能候補</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B40" t="str">
-        <v>環境メタゲームデータ（全体集計）</v>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40" t="str">
-        <v>候補</v>
+        <v>対デッキタイプ別勝率</v>
       </c>
       <c r="E40" t="str">
-        <v>アーキタイプ分布・勝率。コンテンツ価値大</v>
+        <v>候補</v>
+      </c>
+      <c r="F40" t="str">
+        <v>サブスク機能候補。デッキ登録機能後</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B41" t="str">
-        <v>デッキリストからの自動分類（AI）</v>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v>中期</v>
+        <v>月別・タイトル別スタッツ</v>
       </c>
       <c r="E41" t="str">
-        <v>LLM/クラスタリング。派生デッキの再分類にも対応</v>
+        <v>候補</v>
+      </c>
+      <c r="F41" t="str">
+        <v>サブスク機能候補</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>アーキタイプ</v>
+        <v>戦績</v>
       </c>
       <c r="B42" t="str">
-        <v>アーキタイプマスターデータ管理</v>
-      </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="D42" t="str">
-        <v>候補</v>
+        <v>バッジ・実績（100大会参加等）</v>
       </c>
       <c r="E42" t="str">
-        <v>新アーキタイプの追加・統合の運用フロー</v>
+        <v>候補</v>
+      </c>
+      <c r="F42" t="str">
+        <v>エンゲージメント向上</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>デッキ管理（toC）</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v/>
+        <v>アーキタイプ・メタゲーム分析</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B44" t="str">
-        <v>デッキ一覧表示</v>
-      </c>
-      <c r="C44" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
+        <v>自分の使用アーキタイプ登録（任意選択）</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F44" t="str">
+        <v>大会参加時にプルダウンで選択</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B45" t="str">
-        <v>デッキ詳細（カードリスト表示）</v>
-      </c>
-      <c r="C45" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
+        <v>対戦相手のアーキタイプ入力（任意）</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F45" t="str">
+        <v>対戦結果入力時に追加フィールド</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B46" t="str">
-        <v>デッキ編集（カード追加/削除/枚数調整）</v>
-      </c>
-      <c r="C46" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
+        <v>対アーキタイプ別勝率</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F46" t="str">
+        <v>サブスク機能。個人レベルの対面別分析</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B47" t="str">
-        <v>カード検索して追加</v>
-      </c>
-      <c r="C47" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D47" t="str">
-        <v/>
+        <v>環境メタゲームデータ（全体集計）</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F47" t="str">
+        <v>アーキタイプ分布・勝率。コンテンツ価値大</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B48" t="str">
-        <v>デッキ登録上限（無料版3デッキ等）</v>
-      </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
-        <v>候補</v>
+        <v>デッキリストからの自動分類（AI）</v>
       </c>
       <c r="E48" t="str">
-        <v>サブスクで上限解除</v>
+        <v>中期</v>
+      </c>
+      <c r="F48" t="str">
+        <v>LLM/クラスタリング</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>デッキ</v>
+        <v>アーキタイプ</v>
       </c>
       <c r="B49" t="str">
-        <v>デッキレシピ共有（SNS/リンク）</v>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v>候補</v>
+        <v>アーキタイプマスターデータ管理</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F49" t="str">
+        <v>新アーキタイプの追加・統合の運用フロー</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>デッキ</v>
-      </c>
-      <c r="B50" t="str">
-        <v>公開デッキレシピ検索</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E50" t="str">
-        <v>コミュニティ機能</v>
+        <v>デッキ管理（toC）</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B51" t="str">
-        <v/>
-      </c>
-      <c r="C51" t="str">
-        <v/>
+        <v>デッキ一覧表示</v>
       </c>
       <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B52" t="str">
-        <v>プロフィール表示</v>
-      </c>
-      <c r="C52" t="str">
-        <v>✓</v>
+        <v>デッキ詳細（カードリスト表示）</v>
       </c>
       <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v>名前・アバター</v>
+        <v>✓</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B53" t="str">
-        <v>プロフィール編集</v>
-      </c>
-      <c r="C53" t="str">
-        <v>✓</v>
+        <v>デッキ編集（カード追加/削除/枚数調整）</v>
       </c>
       <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B54" t="str">
-        <v>通知設定</v>
-      </c>
-      <c r="C54" t="str">
-        <v>✓</v>
+        <v>カード検索して追加</v>
       </c>
       <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B55" t="str">
-        <v>メーカーID登録（ポケカ等）</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v>Phase1</v>
+        <v>デッキ登録上限（無料版3デッキ等）</v>
       </c>
       <c r="E55" t="str">
-        <v>招待制大会エビデンス用。任意入力</v>
+        <v>候補</v>
+      </c>
+      <c r="F55" t="str">
+        <v>サブスクで上限解除</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B56" t="str">
-        <v>外部ツールID登録（トナメル等）</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v>Phase1</v>
+        <v>デッキレシピ共有（SNS/リンク）</v>
       </c>
       <c r="E56" t="str">
-        <v>スクショ/API連携時の突合用</v>
+        <v>候補</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>アカウント</v>
+        <v>デッキ</v>
       </c>
       <c r="B57" t="str">
-        <v>対応タイトル設定</v>
-      </c>
-      <c r="C57" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D57" t="str">
-        <v/>
+        <v>公開デッキレシピ検索</v>
       </c>
       <c r="E57" t="str">
-        <v>興味のあるTCGタイトル選択 / TCGゲームアイコンとしてホーム・プロフィールに実装</v>
+        <v>候補</v>
+      </c>
+      <c r="F57" t="str">
+        <v>コミュニティ機能</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
         <v>アカウント</v>
       </c>
-      <c r="B58" t="str">
-        <v>サブスク管理</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E58" t="str">
-        <v>月額500円の課金管理</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SNS・コミュニティ（Strava参考・新規）</v>
+        <v>アカウント</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Googleログイン</v>
       </c>
       <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
+        <v>✓</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Supabase Auth連携</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B60" t="str">
-        <v>ホームフィード（フォロー中の大会結果）</v>
-      </c>
-      <c r="C60" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D60" t="str">
-        <v/>
+        <v>LINEログイン</v>
       </c>
       <c r="E60" t="str">
-        <v>Strava Home相当。核心機能 / フォロー中の大会結果フィード実装済み</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>カスタムOIDCプロバイダー</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B61" t="str">
-        <v>Kudos的リアクション（大会結果へ）</v>
+        <v>プロフィール表示</v>
       </c>
       <c r="C61" t="str">
         <v>✓</v>
       </c>
       <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61" t="str">
-        <v>「大会出る→記録残る→見てもらえる」ループ / GG!に名称変更して実装。X・Instagram共有ボタンも追加</v>
+        <v>✓</v>
+      </c>
+      <c r="F61" t="str">
+        <v>名前・アバター・推しショップ・TCG選択</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B62" t="str">
-        <v>フォロー/フォロワー</v>
+        <v>プロフィール編集</v>
       </c>
       <c r="C62" t="str">
         <v>✓</v>
       </c>
       <c r="D62" t="str">
-        <v/>
-      </c>
-      <c r="E62" t="str">
-        <v>フォロー・フォロワー管理実装済み</v>
+        <v>✓</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Supabase DB保存・初回設定画面</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B63" t="str">
-        <v>大会結果のSNSシェア</v>
+        <v>ログアウト</v>
       </c>
       <c r="C63" t="str">
         <v>✓</v>
-      </c>
-      <c r="D63" t="str">
-        <v/>
-      </c>
-      <c r="E63" t="str">
-        <v>X/LINE等への外部共有 / X・Instagram対応（キャプション自動生成）</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B64" t="str">
-        <v>大会結果画像の自動生成→X投稿</v>
-      </c>
-      <c r="C64" t="str">
-        <v>✓</v>
+        <v>通知設定</v>
       </c>
       <c r="D64" t="str">
-        <v/>
-      </c>
-      <c r="E64" t="str">
-        <v>最終成績＋ラウンド毎勝敗＋相手アーキタイプを1枚絵に / X投稿+Instagram用キャプション自動生成実装済み</v>
+        <v>✓</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B65" t="str">
-        <v>デッキリスト画像の自動生成→X投稿</v>
-      </c>
-      <c r="C65" t="str">
-        <v/>
-      </c>
-      <c r="D65" t="str">
-        <v>候補</v>
+        <v>メーカーID登録（ポケカ等）</v>
       </c>
       <c r="E65" t="str">
-        <v>結果画像とセットで2枚投稿。ブランド露出</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F65" t="str">
+        <v>招待制大会エビデンス用。任意入力</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B66" t="str">
-        <v>参加表明（「行くよ」宣言）</v>
-      </c>
-      <c r="C66" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
+        <v>外部ツールID登録（トナメル等）</v>
       </c>
       <c r="E66" t="str">
-        <v>予約とは別。友達と一緒に行く動機づけ / 行くよ！宣言 + 予約するボタン + カレンダー連動も実装</v>
+        <v>Phase1</v>
+      </c>
+      <c r="F66" t="str">
+        <v>スクショ/API連携時の突合用</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B67" t="str">
-        <v>友達の参加表明の通知</v>
+        <v>対応タイトル設定</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="D67" t="str">
-        <v/>
-      </c>
-      <c r="E67" t="str">
-        <v/>
+        <v>✓</v>
+      </c>
+      <c r="F67" t="str">
+        <v>プロフィール編集でTCG選択実装</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SNS</v>
+        <v>アカウント</v>
       </c>
       <c r="B68" t="str">
-        <v>大会結果の自動通知（優勝・入賞）</v>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v>候補</v>
+        <v>サブスク管理</v>
       </c>
       <c r="E68" t="str">
-        <v>フォロワーに自動で通知</v>
+        <v>候補</v>
+      </c>
+      <c r="F68" t="str">
+        <v>月額500円の課金管理</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SNS</v>
-      </c>
-      <c r="B69" t="str">
-        <v>公開プロフィールページ（ショーケース）</v>
-      </c>
-      <c r="C69" t="str">
-        <v>✓</v>
-      </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v>来訪者向け。スタッツ・大会実績がかっこよく見れる / バッジ・ランキング・X/Instagramシェア対応</v>
+        <v>SNS・コミュニティ（Strava参考・新規）</v>
       </c>
     </row>
     <row r="70">
@@ -1577,16 +1277,13 @@
         <v>SNS</v>
       </c>
       <c r="B70" t="str">
-        <v>店舗クラブ（店舗コミュニティ）</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
+        <v>ホームフィード（フォロー中の大会結果）</v>
       </c>
       <c r="D70" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E70" t="str">
-        <v>Strava Club相当。常連の場</v>
+        <v>✓</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Strava Home相当。核心機能</v>
       </c>
     </row>
     <row r="71">
@@ -1594,16 +1291,13 @@
         <v>SNS</v>
       </c>
       <c r="B71" t="str">
-        <v>クラブ内リーダーボード</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
+        <v>Kudos的リアクション（大会結果へ）</v>
       </c>
       <c r="D71" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E71" t="str">
-        <v>店舗ごとの常連ランキング</v>
+        <v>✓</v>
+      </c>
+      <c r="F71" t="str">
+        <v>GG!に名称変更。X・Instagram共有ボタンも追加</v>
       </c>
     </row>
     <row r="72">
@@ -1611,16 +1305,13 @@
         <v>SNS</v>
       </c>
       <c r="B72" t="str">
-        <v>クラブ内投稿・告知</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
+        <v>フォロー/フォロワー</v>
       </c>
       <c r="D72" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E72" t="str">
-        <v>店舗からの情報発信</v>
+        <v>✓</v>
+      </c>
+      <c r="F72" t="str">
+        <v>フォロー・フォロワー管理実装済み</v>
       </c>
     </row>
     <row r="73">
@@ -1628,16 +1319,13 @@
         <v>SNS</v>
       </c>
       <c r="B73" t="str">
-        <v>タイトル別コミュニティ</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
+        <v>大会結果のSNSシェア</v>
       </c>
       <c r="D73" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E73" t="str">
-        <v>ポケカ勢/デュエマ勢等のグルーピング</v>
+        <v>✓</v>
+      </c>
+      <c r="F73" t="str">
+        <v>X・Instagram対応（キャプション自動生成）</v>
       </c>
     </row>
     <row r="74">
@@ -1645,16 +1333,13 @@
         <v>SNS</v>
       </c>
       <c r="B74" t="str">
-        <v>チャレンジ機能</v>
-      </c>
-      <c r="C74" t="str">
-        <v>✓</v>
+        <v>大会結果画像の自動生成→X投稿</v>
       </c>
       <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v>「今月10大会参加」等。スポンサード可能 / カテゴリ別（イベント/バトル/SNS）・XP報酬付きで実装</v>
+        <v>✓</v>
+      </c>
+      <c r="F74" t="str">
+        <v>X投稿+Instagram用キャプション自動生成</v>
       </c>
     </row>
     <row r="75">
@@ -1662,16 +1347,13 @@
         <v>SNS</v>
       </c>
       <c r="B75" t="str">
-        <v>スポンサード・チャレンジ</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v>候補</v>
+        <v>デッキリスト画像の自動生成→X投稿</v>
       </c>
       <c r="E75" t="str">
-        <v>メーカー/サプライメーカー協賛。広告収益</v>
+        <v>候補</v>
+      </c>
+      <c r="F75" t="str">
+        <v>結果画像とセットで2枚投稿。ブランド露出</v>
       </c>
     </row>
     <row r="76">
@@ -1679,16 +1361,13 @@
         <v>SNS</v>
       </c>
       <c r="B76" t="str">
-        <v>店舗×タイトル別ローカルランキング</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
+        <v>参加表明（「行くよ」宣言）</v>
       </c>
       <c r="D76" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E76" t="str">
-        <v>Stravaセグメント的。場所×タイトル</v>
+        <v>✓</v>
+      </c>
+      <c r="F76" t="str">
+        <v>行くよ！宣言 + 予約するボタン + カレンダー連動</v>
       </c>
     </row>
     <row r="77">
@@ -1696,463 +1375,548 @@
         <v>SNS</v>
       </c>
       <c r="B77" t="str">
-        <v>プレイヤープロフィール公開設定</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>候補</v>
+        <v>友達の参加表明の通知</v>
       </c>
       <c r="E77" t="str">
-        <v>公開/フォロワー限定/非公開の選択</v>
+        <v>候補</v>
+      </c>
+      <c r="F77" t="str">
+        <v>「○○さんも行くよ」で参加率向上</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>店舗向け（toB）</v>
+        <v>SNS</v>
       </c>
       <c r="B78" t="str">
-        <v/>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v/>
+        <v>大会結果の自動通知（優勝・入賞）</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F78" t="str">
+        <v>フォロワーに自動で通知</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B79" t="str">
-        <v>大会作成→TCGマイスター連携</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
+        <v>公開プロフィールページ（ショーケース）</v>
       </c>
       <c r="D79" t="str">
-        <v>リリース時</v>
-      </c>
-      <c r="E79" t="str">
-        <v>バックエンド連携</v>
+        <v>✓</v>
+      </c>
+      <c r="F79" t="str">
+        <v>バッジ・ランキング・X/Instagramシェア対応</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B80" t="str">
-        <v>参加者管理（当日運営）</v>
-      </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v>リリース時</v>
+        <v>店舗クラブ（店舗コミュニティ）</v>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Strava Club相当。常連の場</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B81" t="str">
-        <v>顧客データ自動蓄積（CRM基盤）</v>
-      </c>
-      <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="D81" t="str">
-        <v>リリース時</v>
+        <v>クラブ内リーダーボード</v>
       </c>
       <c r="E81" t="str">
-        <v>チェックインで自動登録</v>
+        <v>候補</v>
+      </c>
+      <c r="F81" t="str">
+        <v>店舗ごとの常連ランキング</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B82" t="str">
-        <v>大会告知のアプリ内掲載</v>
-      </c>
-      <c r="C82" t="str">
-        <v/>
-      </c>
-      <c r="D82" t="str">
-        <v>リリース時</v>
+        <v>クラブ内投稿・告知</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F82" t="str">
+        <v>店舗からの情報発信</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B83" t="str">
-        <v>基本CRM（参加者履歴閲覧）</v>
-      </c>
-      <c r="C83" t="str">
-        <v/>
-      </c>
-      <c r="D83" t="str">
-        <v>リリース時</v>
+        <v>タイトル別コミュニティ</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F83" t="str">
+        <v>ポケカ勢/デュエマ勢等のグルーピング</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B84" t="str">
-        <v>大会検索時の上位表示（広告枠）</v>
-      </c>
-      <c r="C84" t="str">
-        <v/>
+        <v>チャレンジ機能</v>
       </c>
       <c r="D84" t="str">
-        <v>候補</v>
+        <v>✓</v>
       </c>
       <c r="E84" t="str">
-        <v>従量課金</v>
+        <v>Phase2</v>
+      </c>
+      <c r="F84" t="str">
+        <v>コアループ確立後に追加。カテゴリ別（イベント/バトル/SNS）・XP報酬付き</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B85" t="str">
-        <v>セール情報配信（LINE push通知）</v>
-      </c>
-      <c r="C85" t="str">
-        <v/>
-      </c>
-      <c r="D85" t="str">
-        <v>候補</v>
+        <v>スポンサード・チャレンジ</v>
       </c>
       <c r="E85" t="str">
-        <v>従量課金</v>
+        <v>候補</v>
+      </c>
+      <c r="F85" t="str">
+        <v>メーカー/サプライメーカー協賛。広告収益</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B86" t="str">
-        <v>詳細顧客分析機能</v>
-      </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
-        <v>候補</v>
+        <v>店舗×タイトル別ローカルランキング</v>
       </c>
       <c r="E86" t="str">
-        <v>プロプラン</v>
+        <v>候補</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Stravaセグメント的。場所×タイトル</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>toB</v>
+        <v>SNS</v>
       </c>
       <c r="B87" t="str">
-        <v>予約・デポジット機能</v>
-      </c>
-      <c r="C87" t="str">
-        <v/>
-      </c>
-      <c r="D87" t="str">
-        <v>候補</v>
+        <v>プレイヤープロフィール公開設定</v>
       </c>
       <c r="E87" t="str">
-        <v>プロプラン</v>
+        <v>候補</v>
+      </c>
+      <c r="F87" t="str">
+        <v>公開/フォロワー限定/非公開の選択</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>toB</v>
-      </c>
-      <c r="B88" t="str">
-        <v>買取表・セール情報のLIFF内掲載</v>
-      </c>
-      <c r="C88" t="str">
-        <v/>
-      </c>
-      <c r="D88" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E88" t="str">
-        <v>プロプラン</v>
+        <v>検索</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>toB</v>
+        <v>検索</v>
       </c>
       <c r="B89" t="str">
-        <v>アドバンスカップ予選開催権</v>
-      </c>
-      <c r="C89" t="str">
-        <v/>
+        <v>検索ハブ（3カテゴリ選択）</v>
       </c>
       <c r="D89" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E89" t="str">
-        <v>有料登録店舗限定</v>
+        <v>✓</v>
+      </c>
+      <c r="F89" t="str">
+        <v>ユーザー/デッキ/イベント検索への導線</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>toB</v>
+        <v>検索</v>
       </c>
       <c r="B90" t="str">
-        <v>優良顧客向けプレミアム商品販売</v>
-      </c>
-      <c r="C90" t="str">
-        <v/>
+        <v>ユーザー検索</v>
       </c>
       <c r="D90" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E90" t="str">
-        <v>CRMデータ活用</v>
+        <v>✓</v>
+      </c>
+      <c r="F90" t="str">
+        <v>プレイヤーを名前で探す</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>toB</v>
+        <v>検索</v>
       </c>
       <c r="B91" t="str">
-        <v>通販ショッピングモール</v>
-      </c>
-      <c r="C91" t="str">
-        <v/>
+        <v>デッキ検索</v>
       </c>
       <c r="D91" t="str">
-        <v>中期</v>
-      </c>
-      <c r="E91" t="str">
-        <v>カカクコム型。2年目以降</v>
+        <v>✓</v>
+      </c>
+      <c r="F91" t="str">
+        <v>シェアされたレシピを探す</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>アドバンスカップ（自社大会）</v>
+        <v>検索</v>
       </c>
       <c r="B92" t="str">
-        <v/>
-      </c>
-      <c r="C92" t="str">
-        <v/>
+        <v>イベント検索</v>
       </c>
       <c r="D92" t="str">
-        <v/>
-      </c>
-      <c r="E92" t="str">
-        <v/>
+        <v>✓</v>
+      </c>
+      <c r="F92" t="str">
+        <v>大会・ジムバトルを探す</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>大会</v>
-      </c>
-      <c r="B93" t="str">
-        <v>店舗予選→地区大会→グランドチャンピオンシップ</v>
-      </c>
-      <c r="C93" t="str">
-        <v/>
-      </c>
-      <c r="D93" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E93" t="str">
-        <v>3層構造</v>
+        <v>ランキング</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>大会</v>
+        <v>ランキング</v>
       </c>
       <c r="B94" t="str">
-        <v>招待制大会（戦績ベース）</v>
-      </c>
-      <c r="C94" t="str">
-        <v/>
+        <v>戦績タブ上部にランキング表示</v>
       </c>
       <c r="D94" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E94" t="str">
-        <v>アドバンス上の戦績が参加条件</v>
+        <v>✓</v>
+      </c>
+      <c r="F94" t="str">
+        <v>全国/エリアトグル・TOP5・自分の順位ハイライト</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>大会</v>
+        <v>ランキング</v>
       </c>
       <c r="B95" t="str">
-        <v>ローンチ時：スクショ＋メーカーID条件</v>
-      </c>
-      <c r="C95" t="str">
-        <v/>
+        <v>ランキング全員表示</v>
       </c>
       <c r="D95" t="str">
-        <v>Phase1</v>
-      </c>
-      <c r="E95" t="str">
-        <v>初期のエビデンス確保</v>
+        <v>✓</v>
+      </c>
+      <c r="F95" t="str">
+        <v>全ランキング一覧ページ</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>大会</v>
-      </c>
-      <c r="B96" t="str">
-        <v>スポンサーシップ管理</v>
-      </c>
-      <c r="C96" t="str">
-        <v/>
-      </c>
-      <c r="D96" t="str">
-        <v>候補</v>
-      </c>
-      <c r="E96" t="str">
-        <v>協賛費の管理</v>
+        <v>店舗向け（toB）</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>toB</v>
       </c>
       <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v/>
-      </c>
-      <c r="D97" t="str">
-        <v/>
+        <v>大会作成→TCGマイスター連携</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>Phase2</v>
+      </c>
+      <c r="F97" t="str">
+        <v>バックエンド連携</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>集計</v>
+        <v>toB</v>
       </c>
       <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v/>
-      </c>
-      <c r="D98" t="str">
-        <v/>
+        <v>参加者管理（当日運営）</v>
       </c>
       <c r="E98" t="str">
-        <v/>
+        <v>Phase2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>モック実装済</v>
-      </c>
-      <c r="B99">
-        <v>33</v>
-      </c>
-      <c r="C99" t="str">
-        <v/>
-      </c>
-      <c r="D99" t="str">
-        <v/>
+        <v>toB</v>
+      </c>
+      <c r="B99" t="str">
+        <v>顧客データ自動蓄積（CRM基盤）</v>
       </c>
       <c r="E99" t="str">
-        <v/>
+        <v>Phase2</v>
+      </c>
+      <c r="F99" t="str">
+        <v>チェックインで自動登録</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Phase1（実装予定）</v>
-      </c>
-      <c r="B100">
-        <v>5</v>
-      </c>
-      <c r="C100" t="str">
-        <v/>
-      </c>
-      <c r="D100" t="str">
-        <v/>
+        <v>toB</v>
+      </c>
+      <c r="B100" t="str">
+        <v>大会告知のアプリ内掲載</v>
       </c>
       <c r="E100" t="str">
-        <v/>
+        <v>Phase2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>リリース時（toB）</v>
-      </c>
-      <c r="B101">
-        <v>5</v>
-      </c>
-      <c r="C101" t="str">
-        <v/>
-      </c>
-      <c r="D101" t="str">
-        <v/>
+        <v>toB</v>
+      </c>
+      <c r="B101" t="str">
+        <v>基本CRM（参加者履歴閲覧）</v>
       </c>
       <c r="E101" t="str">
-        <v/>
+        <v>Phase2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>実装検討（候補）</v>
-      </c>
-      <c r="B102">
-        <v>50</v>
-      </c>
-      <c r="C102" t="str">
-        <v/>
-      </c>
-      <c r="D102" t="str">
-        <v/>
+        <v>toB</v>
+      </c>
+      <c r="B102" t="str">
+        <v>大会検索時の上位表示（広告枠）</v>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>候補</v>
+      </c>
+      <c r="F102" t="str">
+        <v>従量課金</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B103" t="str">
+        <v>セール情報配信（LINE push通知）</v>
+      </c>
+      <c r="E103" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F103" t="str">
+        <v>従量課金</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B104" t="str">
+        <v>詳細顧客分析機能</v>
+      </c>
+      <c r="E104" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F104" t="str">
+        <v>プロプラン</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B105" t="str">
+        <v>予約・デポジット機能</v>
+      </c>
+      <c r="E105" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F105" t="str">
+        <v>プロプラン</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B106" t="str">
+        <v>買取表・セール情報のLIFF内掲載</v>
+      </c>
+      <c r="E106" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F106" t="str">
+        <v>プロプラン</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B107" t="str">
+        <v>アドバンスカップ予選開催権</v>
+      </c>
+      <c r="E107" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F107" t="str">
+        <v>有料登録店舗限定</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B108" t="str">
+        <v>優良顧客向けプレミアム商品販売</v>
+      </c>
+      <c r="E108" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F108" t="str">
+        <v>CRMデータ活用</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>toB</v>
+      </c>
+      <c r="B109" t="str">
+        <v>通販ショッピングモール</v>
+      </c>
+      <c r="E109" t="str">
         <v>中期</v>
       </c>
-      <c r="B103">
+      <c r="F109" t="str">
+        <v>カカクコム型。2年目以降</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>アドバンスカップ（自社大会）</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>大会</v>
+      </c>
+      <c r="B111" t="str">
+        <v>店舗予選→地区大会→グランドチャンピオンシップ</v>
+      </c>
+      <c r="E111" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F111" t="str">
+        <v>3層構造</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>大会</v>
+      </c>
+      <c r="B112" t="str">
+        <v>招待制大会（戦績ベース）</v>
+      </c>
+      <c r="E112" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F112" t="str">
+        <v>アドバンス上の戦績が参加条件</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>大会</v>
+      </c>
+      <c r="B113" t="str">
+        <v>ローンチ時：スクショ＋メーカーID条件</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Phase1</v>
+      </c>
+      <c r="F113" t="str">
+        <v>初期のエビデンス確保</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>大会</v>
+      </c>
+      <c r="B114" t="str">
+        <v>スポンサーシップ管理</v>
+      </c>
+      <c r="E114" t="str">
+        <v>候補</v>
+      </c>
+      <c r="F114" t="str">
+        <v>協賛費の管理</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>集計</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>本番実装済</v>
+      </c>
+      <c r="B117" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>モック実装済</v>
+      </c>
+      <c r="B118" t="str">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Phase1</v>
+      </c>
+      <c r="B119" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Phase2（toB）</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>実装検討（候補）</v>
+      </c>
+      <c r="B121" t="str">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>中期</v>
+      </c>
+      <c r="B122" t="str">
         <v>2</v>
       </c>
-      <c r="C103" t="str">
-        <v/>
-      </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F122"/>
   </ignoredErrors>
 </worksheet>
 </file>